--- a/docs/samples/import_khcn.xlsx
+++ b/docs/samples/import_khcn.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sangn\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E719F13E-1909-486F-9004-8F00A29AAE5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F405FC6D-19E0-4096-AA2F-DF84627C489C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A1832578-3BF3-434D-A9A0-82720227E8B8}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1475" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1623" uniqueCount="340">
   <si>
     <t>assessmentCode</t>
   </si>
@@ -973,6 +973,96 @@
   </si>
   <si>
     <t>planNote</t>
+  </si>
+  <si>
+    <t>STT</t>
+  </si>
+  <si>
+    <t>groupLv2Name</t>
+  </si>
+  <si>
+    <t>groupLv3Name</t>
+  </si>
+  <si>
+    <t>PHÁT TRIỂN THỂ CHẤT</t>
+  </si>
+  <si>
+    <t>vận động thô</t>
+  </si>
+  <si>
+    <t>vận động tinh</t>
+  </si>
+  <si>
+    <t>PHÁT TRIỂN NHẬN THỨC</t>
+  </si>
+  <si>
+    <t>Nhận biết</t>
+  </si>
+  <si>
+    <t>Khám phá khoa học</t>
+  </si>
+  <si>
+    <t>Khám phá xã hội</t>
+  </si>
+  <si>
+    <t>PHÁT TRIỂN NGÔN NGỮ</t>
+  </si>
+  <si>
+    <t>Ngôn ngữ tiếp nhận</t>
+  </si>
+  <si>
+    <t>Ngôn ngữ diễn đạt (nói)</t>
+  </si>
+  <si>
+    <t>CÁ NHÂN VÀ XÃ HỘI</t>
+  </si>
+  <si>
+    <t>Kỹ năng giao tiếp - tương tác - chơi đùa</t>
+  </si>
+  <si>
+    <t>TIỀN TIỂU HỌC</t>
+  </si>
+  <si>
+    <t>TOÁN</t>
+  </si>
+  <si>
+    <t>Ngôn ngữ tiếp nhận: (khả năng nghe hiểu lời nói)</t>
+  </si>
+  <si>
+    <t>Kỹ năng tự lập (Tự phục vụ)</t>
+  </si>
+  <si>
+    <t>Đáp ứng yêu cầu với từ bổ nghĩa</t>
+  </si>
+  <si>
+    <t>TIẾNG VIỆT</t>
+  </si>
+  <si>
+    <t>vđ thô</t>
+  </si>
+  <si>
+    <t>vđ tinh</t>
+  </si>
+  <si>
+    <t>Đáp ứng đặc điểm ngữ pháp</t>
+  </si>
+  <si>
+    <t>Đáp ứng yêu cầu liên quan với từ chỉ hành động</t>
+  </si>
+  <si>
+    <t>Lựa chọn giữa các khả năng: vật và tranh</t>
+  </si>
+  <si>
+    <t>Làm quen với toán</t>
+  </si>
+  <si>
+    <t>Tự phục vụ</t>
+  </si>
+  <si>
+    <t>Lq với toán</t>
+  </si>
+  <si>
+    <t>LQ với toán</t>
   </si>
 </sst>
 </file>
@@ -1408,7 +1498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A48917E2-3D0D-4EA4-B002-2CFB07DFCE98}">
-  <dimension ref="A1:G998"/>
+  <dimension ref="A1:J998"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
@@ -1417,7 +1507,7 @@
     <col min="6" max="7" width="15" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>308</v>
       </c>
@@ -1439,8 +1529,17 @@
       <c r="G1" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H1" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>286</v>
       </c>
@@ -1459,8 +1558,17 @@
       <c r="G2" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2" t="s">
+        <v>313</v>
+      </c>
+      <c r="J2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>286</v>
       </c>
@@ -1479,8 +1587,11 @@
       <c r="G3" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C4" s="4" t="s">
         <v>35</v>
       </c>
@@ -1496,8 +1607,11 @@
       <c r="G4" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C5" s="3" t="s">
         <v>36</v>
       </c>
@@ -1513,8 +1627,14 @@
       <c r="G5" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C6" s="4" t="s">
         <v>37</v>
       </c>
@@ -1530,8 +1650,11 @@
       <c r="G6" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C7" s="3" t="s">
         <v>38</v>
       </c>
@@ -1547,8 +1670,11 @@
       <c r="G7" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C8" s="4" t="s">
         <v>39</v>
       </c>
@@ -1564,8 +1690,11 @@
       <c r="G8" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C9" s="3" t="s">
         <v>40</v>
       </c>
@@ -1581,8 +1710,11 @@
       <c r="G9" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>287</v>
       </c>
@@ -1601,8 +1733,17 @@
       <c r="G10" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" t="s">
+        <v>316</v>
+      </c>
+      <c r="J10" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>286</v>
       </c>
@@ -1621,8 +1762,11 @@
       <c r="G11" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>286</v>
       </c>
@@ -1641,8 +1785,11 @@
       <c r="G12" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>286</v>
       </c>
@@ -1661,8 +1808,14 @@
       <c r="G13" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H13">
+        <v>4</v>
+      </c>
+      <c r="J13" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>286</v>
       </c>
@@ -1681,8 +1834,14 @@
       <c r="G14" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H14">
+        <v>5</v>
+      </c>
+      <c r="J14" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>286</v>
       </c>
@@ -1701,8 +1860,17 @@
       <c r="G15" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15" t="s">
+        <v>320</v>
+      </c>
+      <c r="J15" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>286</v>
       </c>
@@ -1721,8 +1889,14 @@
       <c r="G16" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="J16" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>286</v>
       </c>
@@ -1741,8 +1915,11 @@
       <c r="G17" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>286</v>
       </c>
@@ -1761,8 +1938,11 @@
       <c r="G18" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>286</v>
       </c>
@@ -1781,8 +1961,11 @@
       <c r="G19" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>286</v>
       </c>
@@ -1801,8 +1984,11 @@
       <c r="G20" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>286</v>
       </c>
@@ -1821,8 +2007,11 @@
       <c r="G21" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H21">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>286</v>
       </c>
@@ -1841,8 +2030,11 @@
       <c r="G22" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H22">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>286</v>
       </c>
@@ -1861,8 +2053,17 @@
       <c r="G23" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23" t="s">
+        <v>323</v>
+      </c>
+      <c r="J23" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>286</v>
       </c>
@@ -1881,8 +2082,11 @@
       <c r="G24" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>287</v>
       </c>
@@ -1901,8 +2105,11 @@
       <c r="G25" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>286</v>
       </c>
@@ -1921,8 +2128,17 @@
       <c r="G26" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26" t="s">
+        <v>325</v>
+      </c>
+      <c r="J26" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>286</v>
       </c>
@@ -1941,8 +2157,11 @@
       <c r="G27" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>286</v>
       </c>
@@ -1961,8 +2180,11 @@
       <c r="G28" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>286</v>
       </c>
@@ -1981,8 +2203,11 @@
       <c r="G29" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H29">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>286</v>
       </c>
@@ -2001,8 +2226,11 @@
       <c r="G30" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>286</v>
       </c>
@@ -2021,8 +2249,11 @@
       <c r="G31" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H31">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C32" s="4" t="s">
         <v>63</v>
       </c>
@@ -2038,8 +2269,17 @@
       <c r="G32" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H32">
+        <v>1</v>
+      </c>
+      <c r="I32" t="s">
+        <v>313</v>
+      </c>
+      <c r="J32" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>286</v>
       </c>
@@ -2058,8 +2298,11 @@
       <c r="G33" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C34" s="4" t="s">
         <v>67</v>
       </c>
@@ -2075,8 +2318,11 @@
       <c r="G34" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H34">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C35" s="3" t="s">
         <v>14</v>
       </c>
@@ -2092,8 +2338,14 @@
       <c r="G35" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="J35" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C36" s="4" t="s">
         <v>68</v>
       </c>
@@ -2109,8 +2361,11 @@
       <c r="G36" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C37" s="3" t="s">
         <v>69</v>
       </c>
@@ -2126,8 +2381,11 @@
       <c r="G37" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H37">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C38" s="4" t="s">
         <v>70</v>
       </c>
@@ -2143,8 +2401,11 @@
       <c r="G38" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H38">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C39" s="3" t="s">
         <v>71</v>
       </c>
@@ -2160,8 +2421,11 @@
       <c r="G39" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C40" s="4" t="s">
         <v>72</v>
       </c>
@@ -2177,8 +2441,17 @@
       <c r="G40" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H40">
+        <v>1</v>
+      </c>
+      <c r="I40" t="s">
+        <v>316</v>
+      </c>
+      <c r="J40" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C41" s="3" t="s">
         <v>7</v>
       </c>
@@ -2194,8 +2467,11 @@
       <c r="G41" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C42" s="4" t="s">
         <v>73</v>
       </c>
@@ -2211,8 +2487,11 @@
       <c r="G42" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H42">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C43" s="3" t="s">
         <v>74</v>
       </c>
@@ -2228,8 +2507,11 @@
       <c r="G43" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H43">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C44" s="4" t="s">
         <v>75</v>
       </c>
@@ -2245,8 +2527,17 @@
       <c r="G44" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H44">
+        <v>1</v>
+      </c>
+      <c r="I44" t="s">
+        <v>320</v>
+      </c>
+      <c r="J44" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C45" s="3" t="s">
         <v>76</v>
       </c>
@@ -2262,8 +2553,11 @@
       <c r="G45" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C46" s="4" t="s">
         <v>77</v>
       </c>
@@ -2279,8 +2573,14 @@
       <c r="G46" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H46">
+        <v>1</v>
+      </c>
+      <c r="J46" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C47" s="3" t="s">
         <v>78</v>
       </c>
@@ -2296,8 +2596,11 @@
       <c r="G47" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H47">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C48" s="4" t="s">
         <v>79</v>
       </c>
@@ -2313,8 +2616,11 @@
       <c r="G48" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H48">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C49" s="3" t="s">
         <v>80</v>
       </c>
@@ -2330,8 +2636,11 @@
       <c r="G49" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H49">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C50" s="4" t="s">
         <v>81</v>
       </c>
@@ -2347,8 +2656,11 @@
       <c r="G50" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H50">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>287</v>
       </c>
@@ -2370,8 +2682,11 @@
       <c r="G51" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H51">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>287</v>
       </c>
@@ -2390,8 +2705,11 @@
       <c r="G52" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H52">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>287</v>
       </c>
@@ -2410,8 +2728,11 @@
       <c r="G53" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H53">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>287</v>
       </c>
@@ -2430,8 +2751,11 @@
       <c r="G54" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H54">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>287</v>
       </c>
@@ -2453,8 +2777,11 @@
       <c r="G55" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H55">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>290</v>
       </c>
@@ -2476,8 +2803,11 @@
       <c r="G56" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H56">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C57" s="3" t="s">
         <v>87</v>
       </c>
@@ -2493,8 +2823,17 @@
       <c r="G57" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H57">
+        <v>1</v>
+      </c>
+      <c r="I57" t="s">
+        <v>323</v>
+      </c>
+      <c r="J57" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C58" s="4" t="s">
         <v>22</v>
       </c>
@@ -2510,8 +2849,11 @@
       <c r="G58" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H58">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C59" s="3" t="s">
         <v>88</v>
       </c>
@@ -2527,8 +2869,11 @@
       <c r="G59" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H59">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C60" s="4" t="s">
         <v>28</v>
       </c>
@@ -2544,8 +2889,14 @@
       <c r="G60" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H60">
+        <v>1</v>
+      </c>
+      <c r="J60" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C61" s="3" t="s">
         <v>29</v>
       </c>
@@ -2561,8 +2912,11 @@
       <c r="G61" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H61">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C62" s="4" t="s">
         <v>30</v>
       </c>
@@ -2578,8 +2932,11 @@
       <c r="G62" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H62">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>287</v>
       </c>
@@ -2601,8 +2958,11 @@
       <c r="G63" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H63">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>286</v>
       </c>
@@ -2621,8 +2981,17 @@
       <c r="G64" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H64">
+        <v>1</v>
+      </c>
+      <c r="I64" t="s">
+        <v>313</v>
+      </c>
+      <c r="J64" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C65" s="3" t="s">
         <v>67</v>
       </c>
@@ -2638,8 +3007,11 @@
       <c r="G65" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H65">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C66" s="4" t="s">
         <v>114</v>
       </c>
@@ -2655,8 +3027,11 @@
       <c r="G66" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H66">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C67" s="3" t="s">
         <v>115</v>
       </c>
@@ -2672,8 +3047,14 @@
       <c r="G67" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H67">
+        <v>1</v>
+      </c>
+      <c r="J67" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C68" s="4" t="s">
         <v>116</v>
       </c>
@@ -2689,8 +3070,11 @@
       <c r="G68" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C69" s="3" t="s">
         <v>117</v>
       </c>
@@ -2706,8 +3090,11 @@
       <c r="G69" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H69">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>286</v>
       </c>
@@ -2726,8 +3113,11 @@
       <c r="G70" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H70">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C71" s="3" t="s">
         <v>119</v>
       </c>
@@ -2743,8 +3133,11 @@
       <c r="G71" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H71">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C72" s="4" t="s">
         <v>120</v>
       </c>
@@ -2760,8 +3153,11 @@
       <c r="G72" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H72">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C73" s="3" t="s">
         <v>121</v>
       </c>
@@ -2777,8 +3173,11 @@
       <c r="G73" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H73">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C74" s="4" t="s">
         <v>122</v>
       </c>
@@ -2794,8 +3193,11 @@
       <c r="G74" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H74">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C75" s="3" t="s">
         <v>123</v>
       </c>
@@ -2811,8 +3213,11 @@
       <c r="G75" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H75">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C76" s="4" t="s">
         <v>124</v>
       </c>
@@ -2828,8 +3233,11 @@
       <c r="G76" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H76">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C77" s="3" t="s">
         <v>125</v>
       </c>
@@ -2845,8 +3253,11 @@
       <c r="G77" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H77">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C78" s="4" t="s">
         <v>126</v>
       </c>
@@ -2862,8 +3273,11 @@
       <c r="G78" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H78">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>286</v>
       </c>
@@ -2882,8 +3296,17 @@
       <c r="G79" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H79">
+        <v>1</v>
+      </c>
+      <c r="I79" t="s">
+        <v>316</v>
+      </c>
+      <c r="J79" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C80" s="4" t="s">
         <v>16</v>
       </c>
@@ -2899,8 +3322,11 @@
       <c r="G80" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H80">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C81" s="3" t="s">
         <v>127</v>
       </c>
@@ -2916,8 +3342,17 @@
       <c r="G81" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H81">
+        <v>1</v>
+      </c>
+      <c r="I81" t="s">
+        <v>320</v>
+      </c>
+      <c r="J81" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C82" s="4" t="s">
         <v>128</v>
       </c>
@@ -2933,8 +3368,11 @@
       <c r="G82" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H82">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C83" s="3" t="s">
         <v>129</v>
       </c>
@@ -2950,8 +3388,11 @@
       <c r="G83" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H83">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>286</v>
       </c>
@@ -2970,8 +3411,14 @@
       <c r="G84" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H84">
+        <v>1</v>
+      </c>
+      <c r="J84" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>286</v>
       </c>
@@ -2990,8 +3437,11 @@
       <c r="G85" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H85">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C86" s="4" t="s">
         <v>132</v>
       </c>
@@ -3007,8 +3457,11 @@
       <c r="G86" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H86">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C87" s="3" t="s">
         <v>133</v>
       </c>
@@ -3024,8 +3477,11 @@
       <c r="G87" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="88" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H87">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C88" s="4" t="s">
         <v>134</v>
       </c>
@@ -3041,8 +3497,11 @@
       <c r="G88" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H88">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C89" s="3" t="s">
         <v>135</v>
       </c>
@@ -3058,8 +3517,11 @@
       <c r="G89" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="90" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H89">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C90" s="4" t="s">
         <v>17</v>
       </c>
@@ -3075,8 +3537,11 @@
       <c r="G90" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="91" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H90">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C91" s="3" t="s">
         <v>18</v>
       </c>
@@ -3092,8 +3557,11 @@
       <c r="G91" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="92" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H91">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C92" s="4" t="s">
         <v>19</v>
       </c>
@@ -3109,8 +3577,11 @@
       <c r="G92" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="93" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H92">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C93" s="3" t="s">
         <v>11</v>
       </c>
@@ -3126,8 +3597,11 @@
       <c r="G93" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="94" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H93">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C94" s="4" t="s">
         <v>20</v>
       </c>
@@ -3143,8 +3617,11 @@
       <c r="G94" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="95" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H94">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C95" s="1" t="s">
         <v>21</v>
       </c>
@@ -3160,8 +3637,11 @@
       <c r="G95" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="96" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H95">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C96" s="1" t="s">
         <v>136</v>
       </c>
@@ -3177,8 +3657,17 @@
       <c r="G96" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="97" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H96">
+        <v>1</v>
+      </c>
+      <c r="I96" t="s">
+        <v>323</v>
+      </c>
+      <c r="J96" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C97" s="1" t="s">
         <v>137</v>
       </c>
@@ -3194,8 +3683,11 @@
       <c r="G97" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="98" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H97">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C98" s="1" t="s">
         <v>138</v>
       </c>
@@ -3211,8 +3703,11 @@
       <c r="G98" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H98">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C99" s="1" t="s">
         <v>139</v>
       </c>
@@ -3228,8 +3723,11 @@
       <c r="G99" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="100" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H99">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C100" s="1" t="s">
         <v>140</v>
       </c>
@@ -3245,8 +3743,11 @@
       <c r="G100" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="101" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H100">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C101" s="1" t="s">
         <v>141</v>
       </c>
@@ -3262,8 +3763,11 @@
       <c r="G101" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="102" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H101">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C102" s="1" t="s">
         <v>142</v>
       </c>
@@ -3279,8 +3783,11 @@
       <c r="G102" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="103" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H102">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C103" s="1" t="s">
         <v>25</v>
       </c>
@@ -3296,8 +3803,11 @@
       <c r="G103" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="104" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H103">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C104" s="1" t="s">
         <v>26</v>
       </c>
@@ -3313,8 +3823,11 @@
       <c r="G104" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="105" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H104">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C105" s="1" t="s">
         <v>27</v>
       </c>
@@ -3330,8 +3843,11 @@
       <c r="G105" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="106" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H105">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C106" s="1" t="s">
         <v>143</v>
       </c>
@@ -3347,8 +3863,11 @@
       <c r="G106" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="107" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H106">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C107" s="1" t="s">
         <v>144</v>
       </c>
@@ -3364,8 +3883,11 @@
       <c r="G107" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="108" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H107">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C108" s="1" t="s">
         <v>145</v>
       </c>
@@ -3381,8 +3903,11 @@
       <c r="G108" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="109" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H108">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C109" s="1" t="s">
         <v>146</v>
       </c>
@@ -3398,8 +3923,11 @@
       <c r="G109" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="110" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H109">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C110" s="1" t="s">
         <v>147</v>
       </c>
@@ -3415,8 +3943,11 @@
       <c r="G110" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="111" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H110">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C111" s="1" t="s">
         <v>148</v>
       </c>
@@ -3432,8 +3963,14 @@
       <c r="G111" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="112" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H111">
+        <v>1</v>
+      </c>
+      <c r="J111" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>286</v>
       </c>
@@ -3452,8 +3989,11 @@
       <c r="G112" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="113" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H112">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C113" s="1" t="s">
         <v>149</v>
       </c>
@@ -3469,8 +4009,11 @@
       <c r="G113" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="114" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H113">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="114" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C114" s="1" t="s">
         <v>150</v>
       </c>
@@ -3486,8 +4029,11 @@
       <c r="G114" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="115" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H114">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C115" s="1" t="s">
         <v>151</v>
       </c>
@@ -3503,8 +4049,11 @@
       <c r="G115" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="116" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H115">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C116" s="1" t="s">
         <v>152</v>
       </c>
@@ -3520,8 +4069,11 @@
       <c r="G116" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="117" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H116">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="117" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C117" s="1" t="s">
         <v>153</v>
       </c>
@@ -3537,8 +4089,11 @@
       <c r="G117" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="118" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H117">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="118" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C118" s="1" t="s">
         <v>154</v>
       </c>
@@ -3554,8 +4109,11 @@
       <c r="G118" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="119" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H118">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="119" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C119" s="1" t="s">
         <v>155</v>
       </c>
@@ -3571,8 +4129,11 @@
       <c r="G119" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="120" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H119">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="120" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C120" s="1" t="s">
         <v>156</v>
       </c>
@@ -3588,8 +4149,11 @@
       <c r="G120" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="121" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H120">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="121" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C121" s="1" t="s">
         <v>157</v>
       </c>
@@ -3605,8 +4169,11 @@
       <c r="G121" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="122" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H121">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="122" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C122" s="1" t="s">
         <v>158</v>
       </c>
@@ -3622,8 +4189,17 @@
       <c r="G122" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="123" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H122">
+        <v>1</v>
+      </c>
+      <c r="I122" t="s">
+        <v>316</v>
+      </c>
+      <c r="J122" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="123" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C123" s="1" t="s">
         <v>161</v>
       </c>
@@ -3639,8 +4215,11 @@
       <c r="G123" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="124" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H123">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C124" s="1" t="s">
         <v>162</v>
       </c>
@@ -3656,8 +4235,11 @@
       <c r="G124" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="125" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H124">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="125" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C125" s="1" t="s">
         <v>163</v>
       </c>
@@ -3673,8 +4255,11 @@
       <c r="G125" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="126" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H125">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C126" s="1" t="s">
         <v>164</v>
       </c>
@@ -3690,8 +4275,11 @@
       <c r="G126" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="127" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H126">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="127" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C127" s="1" t="s">
         <v>165</v>
       </c>
@@ -3707,8 +4295,17 @@
       <c r="G127" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="128" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H127">
+        <v>1</v>
+      </c>
+      <c r="I127" t="s">
+        <v>320</v>
+      </c>
+      <c r="J127" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="128" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C128" s="1" t="s">
         <v>166</v>
       </c>
@@ -3724,8 +4321,11 @@
       <c r="G128" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="129" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H128">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C129" s="1" t="s">
         <v>167</v>
       </c>
@@ -3741,8 +4341,11 @@
       <c r="G129" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="130" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H129">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C130" s="1" t="s">
         <v>168</v>
       </c>
@@ -3758,8 +4361,11 @@
       <c r="G130" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="131" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H130">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>287</v>
       </c>
@@ -3778,8 +4384,11 @@
       <c r="G131" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="132" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H131">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>287</v>
       </c>
@@ -3801,8 +4410,14 @@
       <c r="G132" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="133" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H132">
+        <v>2</v>
+      </c>
+      <c r="J132" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C133" s="1" t="s">
         <v>171</v>
       </c>
@@ -3818,8 +4433,17 @@
       <c r="G133" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="134" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H133">
+        <v>1</v>
+      </c>
+      <c r="I133" t="s">
+        <v>325</v>
+      </c>
+      <c r="J133" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C134" s="1" t="s">
         <v>172</v>
       </c>
@@ -3835,8 +4459,11 @@
       <c r="G134" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="135" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H134">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C135" s="1" t="s">
         <v>173</v>
       </c>
@@ -3852,8 +4479,11 @@
       <c r="G135" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="136" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H135">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C136" s="1" t="s">
         <v>174</v>
       </c>
@@ -3869,8 +4499,11 @@
       <c r="G136" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="137" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H136">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C137" s="1" t="s">
         <v>175</v>
       </c>
@@ -3886,8 +4519,11 @@
       <c r="G137" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="138" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H137">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C138" s="1" t="s">
         <v>58</v>
       </c>
@@ -3903,8 +4539,11 @@
       <c r="G138" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="139" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H138">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C139" s="1" t="s">
         <v>59</v>
       </c>
@@ -3920,8 +4559,11 @@
       <c r="G139" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="140" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H139">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C140" s="1" t="s">
         <v>60</v>
       </c>
@@ -3937,8 +4579,11 @@
       <c r="G140" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="141" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H140">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C141" s="1" t="s">
         <v>61</v>
       </c>
@@ -3954,8 +4599,11 @@
       <c r="G141" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="142" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H141">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C142" s="1" t="s">
         <v>62</v>
       </c>
@@ -3971,8 +4619,11 @@
       <c r="G142" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="143" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H142">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C143" s="1" t="s">
         <v>176</v>
       </c>
@@ -3988,8 +4639,14 @@
       <c r="G143" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="144" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H143">
+        <v>1</v>
+      </c>
+      <c r="J143" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C144" s="1" t="s">
         <v>177</v>
       </c>
@@ -4005,8 +4662,11 @@
       <c r="G144" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="145" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H144">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C145" s="1" t="s">
         <v>178</v>
       </c>
@@ -4022,8 +4682,11 @@
       <c r="G145" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="146" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H145">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C146" s="1" t="s">
         <v>179</v>
       </c>
@@ -4039,8 +4702,11 @@
       <c r="G146" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="147" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H146">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C147" s="1" t="s">
         <v>180</v>
       </c>
@@ -4056,8 +4722,11 @@
       <c r="G147" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="148" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H147">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C148" s="1" t="s">
         <v>181</v>
       </c>
@@ -4073,8 +4742,11 @@
       <c r="G148" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="149" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H148">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C149" s="1" t="s">
         <v>182</v>
       </c>
@@ -4090,8 +4762,11 @@
       <c r="G149" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="150" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H149">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C150" s="1" t="s">
         <v>183</v>
       </c>
@@ -4107,8 +4782,11 @@
       <c r="G150" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="151" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H150">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C151" s="1" t="s">
         <v>184</v>
       </c>
@@ -4124,8 +4802,11 @@
       <c r="G151" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="152" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H151">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C152" s="1" t="s">
         <v>185</v>
       </c>
@@ -4141,8 +4822,11 @@
       <c r="G152" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="153" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H152">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C153" s="1" t="s">
         <v>186</v>
       </c>
@@ -4158,8 +4842,11 @@
       <c r="G153" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="154" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H153">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C154" s="1" t="s">
         <v>187</v>
       </c>
@@ -4175,8 +4862,11 @@
       <c r="G154" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="155" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H154">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C155" s="1" t="s">
         <v>188</v>
       </c>
@@ -4192,8 +4882,11 @@
       <c r="G155" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="156" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H155">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C156" s="1" t="s">
         <v>189</v>
       </c>
@@ -4209,8 +4902,11 @@
       <c r="G156" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="157" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H156">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C157" s="1" t="s">
         <v>190</v>
       </c>
@@ -4226,8 +4922,11 @@
       <c r="G157" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="158" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H157">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C158" s="1" t="s">
         <v>191</v>
       </c>
@@ -4243,8 +4942,11 @@
       <c r="G158" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="159" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H158">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>286</v>
       </c>
@@ -4263,8 +4965,17 @@
       <c r="G159" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="160" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H159">
+        <v>1</v>
+      </c>
+      <c r="I159" t="s">
+        <v>313</v>
+      </c>
+      <c r="J159" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>286</v>
       </c>
@@ -4283,8 +4994,11 @@
       <c r="G160" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="161" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H160">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>286</v>
       </c>
@@ -4303,8 +5017,14 @@
       <c r="G161" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="162" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H161">
+        <v>1</v>
+      </c>
+      <c r="J161" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>286</v>
       </c>
@@ -4323,8 +5043,11 @@
       <c r="G162" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="163" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H162">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>286</v>
       </c>
@@ -4343,8 +5066,11 @@
       <c r="G163" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="164" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H163">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>286</v>
       </c>
@@ -4363,8 +5089,11 @@
       <c r="G164" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="165" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H164">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>286</v>
       </c>
@@ -4383,8 +5112,11 @@
       <c r="G165" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="166" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H165">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>286</v>
       </c>
@@ -4403,8 +5135,11 @@
       <c r="G166" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="167" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H166">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>286</v>
       </c>
@@ -4423,8 +5158,11 @@
       <c r="G167" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="168" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H167">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>286</v>
       </c>
@@ -4443,8 +5181,17 @@
       <c r="G168" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="169" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H168">
+        <v>1</v>
+      </c>
+      <c r="I168" t="s">
+        <v>316</v>
+      </c>
+      <c r="J168" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>286</v>
       </c>
@@ -4463,8 +5210,11 @@
       <c r="G169" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="170" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H169">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>286</v>
       </c>
@@ -4483,8 +5233,17 @@
       <c r="G170" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="171" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H170">
+        <v>1</v>
+      </c>
+      <c r="I170" t="s">
+        <v>320</v>
+      </c>
+      <c r="J170" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>286</v>
       </c>
@@ -4503,8 +5262,14 @@
       <c r="G171" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="172" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H171">
+        <v>1</v>
+      </c>
+      <c r="J171" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>286</v>
       </c>
@@ -4523,8 +5288,11 @@
       <c r="G172" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="173" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H172">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>286</v>
       </c>
@@ -4543,8 +5311,11 @@
       <c r="G173" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="174" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H173">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>286</v>
       </c>
@@ -4563,8 +5334,11 @@
       <c r="G174" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="175" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H174">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>286</v>
       </c>
@@ -4583,8 +5357,11 @@
       <c r="G175" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="176" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H175">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>286</v>
       </c>
@@ -4603,8 +5380,11 @@
       <c r="G176" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="177" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H176">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>286</v>
       </c>
@@ -4623,8 +5403,11 @@
       <c r="G177" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="178" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H177">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>286</v>
       </c>
@@ -4643,8 +5426,11 @@
       <c r="G178" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="179" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H178">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>286</v>
       </c>
@@ -4663,8 +5449,11 @@
       <c r="G179" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="180" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H179">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>286</v>
       </c>
@@ -4683,8 +5472,11 @@
       <c r="G180" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="181" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H180">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>286</v>
       </c>
@@ -4703,8 +5495,11 @@
       <c r="G181" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="182" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H181">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>286</v>
       </c>
@@ -4723,8 +5518,11 @@
       <c r="G182" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="183" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H182">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>286</v>
       </c>
@@ -4743,8 +5541,17 @@
       <c r="G183" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="184" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H183">
+        <v>1</v>
+      </c>
+      <c r="I183" t="s">
+        <v>323</v>
+      </c>
+      <c r="J183" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>286</v>
       </c>
@@ -4763,8 +5570,11 @@
       <c r="G184" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="185" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H184">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>286</v>
       </c>
@@ -4783,8 +5593,11 @@
       <c r="G185" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="186" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H185">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>286</v>
       </c>
@@ -4803,8 +5616,11 @@
       <c r="G186" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="187" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H186">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>286</v>
       </c>
@@ -4823,8 +5639,11 @@
       <c r="G187" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="188" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H187">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>286</v>
       </c>
@@ -4843,8 +5662,11 @@
       <c r="G188" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="189" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H188">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>286</v>
       </c>
@@ -4863,8 +5685,11 @@
       <c r="G189" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="190" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H189">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>286</v>
       </c>
@@ -4883,8 +5708,11 @@
       <c r="G190" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="191" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H190">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>286</v>
       </c>
@@ -4903,8 +5731,11 @@
       <c r="G191" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="192" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H191">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>286</v>
       </c>
@@ -4923,8 +5754,11 @@
       <c r="G192" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="193" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H192">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>286</v>
       </c>
@@ -4943,8 +5777,11 @@
       <c r="G193" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="194" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H193">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>286</v>
       </c>
@@ -4963,8 +5800,11 @@
       <c r="G194" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="195" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H194">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>286</v>
       </c>
@@ -4983,8 +5823,11 @@
       <c r="G195" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="196" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H195">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>286</v>
       </c>
@@ -5003,8 +5846,11 @@
       <c r="G196" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="197" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H196">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>286</v>
       </c>
@@ -5023,8 +5869,11 @@
       <c r="G197" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="198" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H197">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>286</v>
       </c>
@@ -5043,8 +5892,14 @@
       <c r="G198" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="199" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H198">
+        <v>1</v>
+      </c>
+      <c r="J198" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>286</v>
       </c>
@@ -5063,8 +5918,11 @@
       <c r="G199" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="200" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H199">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>286</v>
       </c>
@@ -5083,8 +5941,11 @@
       <c r="G200" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="201" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H200">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>286</v>
       </c>
@@ -5103,8 +5964,11 @@
       <c r="G201" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="202" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H201">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>286</v>
       </c>
@@ -5123,8 +5987,11 @@
       <c r="G202" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="203" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H202">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>286</v>
       </c>
@@ -5143,8 +6010,11 @@
       <c r="G203" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="204" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H203">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>286</v>
       </c>
@@ -5163,8 +6033,11 @@
       <c r="G204" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="205" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H204">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>286</v>
       </c>
@@ -5183,8 +6056,11 @@
       <c r="G205" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="206" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H205">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>286</v>
       </c>
@@ -5203,8 +6079,11 @@
       <c r="G206" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="207" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H206">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>286</v>
       </c>
@@ -5223,8 +6102,11 @@
       <c r="G207" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="208" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H207">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C208" s="1" t="s">
         <v>111</v>
       </c>
@@ -5240,8 +6122,17 @@
       <c r="G208" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="209" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H208">
+        <v>1</v>
+      </c>
+      <c r="I208" t="s">
+        <v>313</v>
+      </c>
+      <c r="J208" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="209" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C209" s="1" t="s">
         <v>194</v>
       </c>
@@ -5257,8 +6148,11 @@
       <c r="G209" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="210" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H209">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="210" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C210" s="1" t="s">
         <v>115</v>
       </c>
@@ -5274,8 +6168,14 @@
       <c r="G210" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="211" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H210">
+        <v>1</v>
+      </c>
+      <c r="J210" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="211" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C211" s="1" t="s">
         <v>116</v>
       </c>
@@ -5291,8 +6191,11 @@
       <c r="G211" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="212" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H211">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="212" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C212" s="1" t="s">
         <v>195</v>
       </c>
@@ -5308,8 +6211,11 @@
       <c r="G212" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="213" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H212">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="213" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C213" s="1" t="s">
         <v>119</v>
       </c>
@@ -5325,8 +6231,11 @@
       <c r="G213" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="214" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H213">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="214" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C214" s="1" t="s">
         <v>120</v>
       </c>
@@ -5342,8 +6251,11 @@
       <c r="G214" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="215" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H214">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="215" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C215" s="1" t="s">
         <v>123</v>
       </c>
@@ -5359,8 +6271,11 @@
       <c r="G215" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="216" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H215">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="216" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C216" s="1" t="s">
         <v>124</v>
       </c>
@@ -5376,8 +6291,11 @@
       <c r="G216" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="217" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H216">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="217" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C217" s="1" t="s">
         <v>73</v>
       </c>
@@ -5393,8 +6311,17 @@
       <c r="G217" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="218" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H217">
+        <v>1</v>
+      </c>
+      <c r="I217" t="s">
+        <v>316</v>
+      </c>
+      <c r="J217" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="218" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C218" s="1" t="s">
         <v>16</v>
       </c>
@@ -5410,8 +6337,11 @@
       <c r="G218" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="219" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H218">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="219" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C219" s="1" t="s">
         <v>127</v>
       </c>
@@ -5427,8 +6357,17 @@
       <c r="G219" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="220" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H219">
+        <v>1</v>
+      </c>
+      <c r="I219" t="s">
+        <v>320</v>
+      </c>
+      <c r="J219" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="220" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C220" s="1" t="s">
         <v>130</v>
       </c>
@@ -5444,8 +6383,14 @@
       <c r="G220" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="221" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H220">
+        <v>1</v>
+      </c>
+      <c r="J220" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="221" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C221" s="1" t="s">
         <v>131</v>
       </c>
@@ -5461,8 +6406,11 @@
       <c r="G221" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="222" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H221">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="222" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C222" s="1" t="s">
         <v>132</v>
       </c>
@@ -5478,8 +6426,11 @@
       <c r="G222" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="223" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H222">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="223" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C223" s="1" t="s">
         <v>133</v>
       </c>
@@ -5495,8 +6446,11 @@
       <c r="G223" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="224" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H223">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="224" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C224" s="1" t="s">
         <v>134</v>
       </c>
@@ -5512,8 +6466,11 @@
       <c r="G224" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="225" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H224">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="225" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C225" s="1" t="s">
         <v>135</v>
       </c>
@@ -5529,8 +6486,11 @@
       <c r="G225" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="226" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H225">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="226" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C226" s="1" t="s">
         <v>17</v>
       </c>
@@ -5546,8 +6506,11 @@
       <c r="G226" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="227" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H226">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="227" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C227" s="1" t="s">
         <v>18</v>
       </c>
@@ -5563,8 +6526,11 @@
       <c r="G227" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="228" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H227">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="228" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C228" s="1" t="s">
         <v>19</v>
       </c>
@@ -5580,8 +6546,11 @@
       <c r="G228" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="229" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H228">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="229" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C229" s="1" t="s">
         <v>11</v>
       </c>
@@ -5597,8 +6566,11 @@
       <c r="G229" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="230" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H229">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="230" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C230" s="1" t="s">
         <v>20</v>
       </c>
@@ -5614,8 +6586,11 @@
       <c r="G230" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="231" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H230">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="231" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C231" s="1" t="s">
         <v>21</v>
       </c>
@@ -5631,8 +6606,11 @@
       <c r="G231" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="232" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H231">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="232" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C232" s="1" t="s">
         <v>136</v>
       </c>
@@ -5648,8 +6626,17 @@
       <c r="G232" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="233" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H232">
+        <v>1</v>
+      </c>
+      <c r="I232" t="s">
+        <v>323</v>
+      </c>
+      <c r="J232" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="233" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C233" s="1" t="s">
         <v>137</v>
       </c>
@@ -5665,8 +6652,11 @@
       <c r="G233" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="234" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H233">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="234" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C234" s="1" t="s">
         <v>138</v>
       </c>
@@ -5682,8 +6672,11 @@
       <c r="G234" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="235" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H234">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="235" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C235" s="1" t="s">
         <v>139</v>
       </c>
@@ -5699,8 +6692,11 @@
       <c r="G235" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="236" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H235">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="236" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C236" s="1" t="s">
         <v>140</v>
       </c>
@@ -5716,8 +6712,11 @@
       <c r="G236" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="237" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H236">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="237" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C237" s="1" t="s">
         <v>141</v>
       </c>
@@ -5733,8 +6732,11 @@
       <c r="G237" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="238" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H237">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="238" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C238" s="1" t="s">
         <v>142</v>
       </c>
@@ -5750,8 +6752,11 @@
       <c r="G238" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="239" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H238">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="239" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C239" s="1" t="s">
         <v>25</v>
       </c>
@@ -5767,8 +6772,11 @@
       <c r="G239" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="240" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H239">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="240" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C240" s="1" t="s">
         <v>26</v>
       </c>
@@ -5784,8 +6792,11 @@
       <c r="G240" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="241" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H240">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="241" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C241" s="1" t="s">
         <v>27</v>
       </c>
@@ -5801,8 +6812,11 @@
       <c r="G241" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="242" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H241">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="242" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C242" s="1" t="s">
         <v>143</v>
       </c>
@@ -5818,8 +6832,11 @@
       <c r="G242" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="243" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H242">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="243" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C243" s="1" t="s">
         <v>144</v>
       </c>
@@ -5835,8 +6852,11 @@
       <c r="G243" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="244" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H243">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="244" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C244" s="1" t="s">
         <v>145</v>
       </c>
@@ -5852,8 +6872,11 @@
       <c r="G244" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="245" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H244">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="245" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C245" s="1" t="s">
         <v>146</v>
       </c>
@@ -5869,8 +6892,11 @@
       <c r="G245" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="246" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H245">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="246" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C246" s="1" t="s">
         <v>147</v>
       </c>
@@ -5886,8 +6912,11 @@
       <c r="G246" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="247" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H246">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="247" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C247" s="1" t="s">
         <v>148</v>
       </c>
@@ -5903,8 +6932,14 @@
       <c r="G247" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="248" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H247">
+        <v>1</v>
+      </c>
+      <c r="J247" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="248" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C248" s="1" t="s">
         <v>28</v>
       </c>
@@ -5920,8 +6955,11 @@
       <c r="G248" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="249" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H248">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="249" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C249" s="1" t="s">
         <v>149</v>
       </c>
@@ -5937,8 +6975,11 @@
       <c r="G249" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="250" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H249">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="250" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C250" s="1" t="s">
         <v>150</v>
       </c>
@@ -5954,8 +6995,11 @@
       <c r="G250" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="251" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H250">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="251" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C251" s="1" t="s">
         <v>151</v>
       </c>
@@ -5971,8 +7015,11 @@
       <c r="G251" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="252" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H251">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="252" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C252" s="1" t="s">
         <v>152</v>
       </c>
@@ -5988,8 +7035,11 @@
       <c r="G252" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="253" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H252">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="253" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C253" s="1" t="s">
         <v>153</v>
       </c>
@@ -6005,8 +7055,11 @@
       <c r="G253" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="254" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H253">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="254" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C254" s="1" t="s">
         <v>154</v>
       </c>
@@ -6022,8 +7075,11 @@
       <c r="G254" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="255" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H254">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="255" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C255" s="1" t="s">
         <v>155</v>
       </c>
@@ -6039,8 +7095,11 @@
       <c r="G255" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="256" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H255">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="256" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C256" s="1" t="s">
         <v>156</v>
       </c>
@@ -6056,8 +7115,11 @@
       <c r="G256" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="257" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H256">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C257" s="1" t="s">
         <v>198</v>
       </c>
@@ -6073,8 +7135,17 @@
       <c r="G257" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="258" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H257">
+        <v>1</v>
+      </c>
+      <c r="I257" t="s">
+        <v>313</v>
+      </c>
+      <c r="J257" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="258" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C258" s="1" t="s">
         <v>201</v>
       </c>
@@ -6090,8 +7161,11 @@
       <c r="G258" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="259" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H258">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="259" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C259" s="1" t="s">
         <v>202</v>
       </c>
@@ -6107,8 +7181,11 @@
       <c r="G259" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="260" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H259">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="260" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B260" t="s">
         <v>294</v>
       </c>
@@ -6127,8 +7204,14 @@
       <c r="G260" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="261" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H260">
+        <v>1</v>
+      </c>
+      <c r="J260" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="261" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>286</v>
       </c>
@@ -6147,8 +7230,11 @@
       <c r="G261" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="262" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H261">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="262" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>286</v>
       </c>
@@ -6167,8 +7253,11 @@
       <c r="G262" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="263" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H262">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="263" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>286</v>
       </c>
@@ -6187,8 +7276,11 @@
       <c r="G263" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="264" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H263">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="264" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>286</v>
       </c>
@@ -6207,8 +7299,11 @@
       <c r="G264" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="265" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H264">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="265" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C265" s="1" t="s">
         <v>69</v>
       </c>
@@ -6224,8 +7319,11 @@
       <c r="G265" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="266" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H265">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="266" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C266" s="1" t="s">
         <v>205</v>
       </c>
@@ -6241,8 +7339,17 @@
       <c r="G266" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="267" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H266">
+        <v>1</v>
+      </c>
+      <c r="I266" t="s">
+        <v>316</v>
+      </c>
+      <c r="J266" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="267" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C267" s="1" t="s">
         <v>72</v>
       </c>
@@ -6258,8 +7365,11 @@
       <c r="G267" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="268" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H267">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="268" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>286</v>
       </c>
@@ -6278,8 +7388,11 @@
       <c r="G268" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="269" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H268">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="269" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C269" s="1" t="s">
         <v>8</v>
       </c>
@@ -6295,8 +7408,17 @@
       <c r="G269" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="270" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H269">
+        <v>1</v>
+      </c>
+      <c r="I269" t="s">
+        <v>320</v>
+      </c>
+      <c r="J269" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="270" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>286</v>
       </c>
@@ -6318,8 +7440,11 @@
       <c r="G270" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="271" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H270">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="271" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C271" s="1" t="s">
         <v>76</v>
       </c>
@@ -6335,8 +7460,11 @@
       <c r="G271" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="272" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H271">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="272" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C272" s="1" t="s">
         <v>86</v>
       </c>
@@ -6352,8 +7480,14 @@
       <c r="G272" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="273" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H272">
+        <v>1</v>
+      </c>
+      <c r="J272" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="273" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>286</v>
       </c>
@@ -6372,8 +7506,11 @@
       <c r="G273" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="274" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H273">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="274" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>286</v>
       </c>
@@ -6392,8 +7529,11 @@
       <c r="G274" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="275" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H274">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="275" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>286</v>
       </c>
@@ -6412,8 +7552,11 @@
       <c r="G275" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="276" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H275">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="276" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>286</v>
       </c>
@@ -6432,8 +7575,11 @@
       <c r="G276" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="277" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H276">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="277" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>286</v>
       </c>
@@ -6452,8 +7598,11 @@
       <c r="G277" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="278" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H277">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="278" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>286</v>
       </c>
@@ -6472,8 +7621,11 @@
       <c r="G278" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="279" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H278">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="279" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>286</v>
       </c>
@@ -6492,8 +7644,11 @@
       <c r="G279" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="280" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H279">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="280" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>286</v>
       </c>
@@ -6512,8 +7667,11 @@
       <c r="G280" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="281" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H280">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="281" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C281" s="1" t="s">
         <v>210</v>
       </c>
@@ -6529,8 +7687,17 @@
       <c r="G281" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="282" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H281">
+        <v>1</v>
+      </c>
+      <c r="I281" t="s">
+        <v>323</v>
+      </c>
+      <c r="J281" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="282" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C282" s="1" t="s">
         <v>211</v>
       </c>
@@ -6546,8 +7713,11 @@
       <c r="G282" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="283" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H282">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="283" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C283" s="1" t="s">
         <v>212</v>
       </c>
@@ -6563,8 +7733,11 @@
       <c r="G283" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="284" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H283">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="284" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C284" s="1" t="s">
         <v>96</v>
       </c>
@@ -6580,8 +7753,11 @@
       <c r="G284" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="285" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H284">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="285" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>286</v>
       </c>
@@ -6600,8 +7776,11 @@
       <c r="G285" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="286" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H285">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="286" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>286</v>
       </c>
@@ -6620,8 +7799,11 @@
       <c r="G286" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="287" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H286">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="287" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C287" s="1" t="s">
         <v>87</v>
       </c>
@@ -6637,8 +7819,11 @@
       <c r="G287" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="288" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H287">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="288" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>286</v>
       </c>
@@ -6657,8 +7842,14 @@
       <c r="G288" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="289" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H288">
+        <v>1</v>
+      </c>
+      <c r="J288" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="289" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>286</v>
       </c>
@@ -6677,8 +7868,11 @@
       <c r="G289" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="290" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H289">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="290" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C290" s="1" t="s">
         <v>89</v>
       </c>
@@ -6694,8 +7888,11 @@
       <c r="G290" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="291" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H290">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="291" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C291" s="1" t="s">
         <v>213</v>
       </c>
@@ -6711,8 +7908,11 @@
       <c r="G291" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="292" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H291">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="292" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C292" s="1" t="s">
         <v>214</v>
       </c>
@@ -6728,8 +7928,11 @@
       <c r="G292" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="293" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H292">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="293" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C293" s="1" t="s">
         <v>215</v>
       </c>
@@ -6745,8 +7948,11 @@
       <c r="G293" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="294" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H293">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="294" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>286</v>
       </c>
@@ -6765,8 +7971,17 @@
       <c r="G294" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="295" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H294">
+        <v>1</v>
+      </c>
+      <c r="I294" t="s">
+        <v>313</v>
+      </c>
+      <c r="J294" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="295" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C295" s="1" t="s">
         <v>90</v>
       </c>
@@ -6782,8 +7997,11 @@
       <c r="G295" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="296" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H295">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="296" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C296" s="1" t="s">
         <v>36</v>
       </c>
@@ -6799,8 +8017,14 @@
       <c r="G296" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="297" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H296">
+        <v>1</v>
+      </c>
+      <c r="J296" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="297" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>286</v>
       </c>
@@ -6822,8 +8046,17 @@
       <c r="G297" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="298" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H297">
+        <v>1</v>
+      </c>
+      <c r="I297" t="s">
+        <v>316</v>
+      </c>
+      <c r="J297" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="298" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>286</v>
       </c>
@@ -6842,8 +8075,11 @@
       <c r="G298" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="299" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H298">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="299" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>286</v>
       </c>
@@ -6862,8 +8098,11 @@
       <c r="G299" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="300" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H299">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="300" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C300" s="1" t="s">
         <v>222</v>
       </c>
@@ -6879,8 +8118,17 @@
       <c r="G300" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="301" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H300">
+        <v>1</v>
+      </c>
+      <c r="I300" t="s">
+        <v>320</v>
+      </c>
+      <c r="J300" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="301" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C301" s="1" t="s">
         <v>223</v>
       </c>
@@ -6896,8 +8144,11 @@
       <c r="G301" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="302" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H301">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="302" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C302" s="1" t="s">
         <v>224</v>
       </c>
@@ -6913,8 +8164,14 @@
       <c r="G302" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="303" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H302">
+        <v>3</v>
+      </c>
+      <c r="J302" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="303" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>287</v>
       </c>
@@ -6933,8 +8190,14 @@
       <c r="G303" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="304" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H303">
+        <v>4</v>
+      </c>
+      <c r="J303" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="304" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>287</v>
       </c>
@@ -6953,8 +8216,11 @@
       <c r="G304" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="305" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H304">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="305" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C305" s="1" t="s">
         <v>166</v>
       </c>
@@ -6970,8 +8236,14 @@
       <c r="G305" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="306" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H305">
+        <v>6</v>
+      </c>
+      <c r="J305" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="306" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C306" s="1" t="s">
         <v>168</v>
       </c>
@@ -6987,8 +8259,11 @@
       <c r="G306" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="307" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H306">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="307" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>286</v>
       </c>
@@ -7007,8 +8282,17 @@
       <c r="G307" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="308" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H307">
+        <v>1</v>
+      </c>
+      <c r="I307" t="s">
+        <v>325</v>
+      </c>
+      <c r="J307" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="308" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>286</v>
       </c>
@@ -7027,8 +8311,11 @@
       <c r="G308" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="309" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H308">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="309" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C309" s="1" t="s">
         <v>229</v>
       </c>
@@ -7044,8 +8331,17 @@
       <c r="G309" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="310" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H309">
+        <v>1</v>
+      </c>
+      <c r="I309" t="s">
+        <v>313</v>
+      </c>
+      <c r="J309" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="310" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C310" s="1" t="s">
         <v>67</v>
       </c>
@@ -7061,8 +8357,11 @@
       <c r="G310" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="311" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H310">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="311" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C311" s="1" t="s">
         <v>232</v>
       </c>
@@ -7078,8 +8377,11 @@
       <c r="G311" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="312" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H311">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="312" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C312" s="1" t="s">
         <v>233</v>
       </c>
@@ -7095,8 +8397,14 @@
       <c r="G312" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="313" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H312">
+        <v>1</v>
+      </c>
+      <c r="J312" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="313" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C313" s="1" t="s">
         <v>203</v>
       </c>
@@ -7112,8 +8420,11 @@
       <c r="G313" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="314" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H313">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="314" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C314" s="1" t="s">
         <v>234</v>
       </c>
@@ -7129,8 +8440,11 @@
       <c r="G314" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="315" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H314">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="315" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C315" s="1" t="s">
         <v>92</v>
       </c>
@@ -7146,8 +8460,17 @@
       <c r="G315" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="316" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H315">
+        <v>1</v>
+      </c>
+      <c r="I315" t="s">
+        <v>316</v>
+      </c>
+      <c r="J315" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="316" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C316" s="1" t="s">
         <v>235</v>
       </c>
@@ -7163,8 +8486,11 @@
       <c r="G316" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="317" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H316">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="317" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C317" s="1" t="s">
         <v>45</v>
       </c>
@@ -7180,8 +8506,14 @@
       <c r="G317" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="318" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H317">
+        <v>3</v>
+      </c>
+      <c r="J317" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="318" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C318" s="1" t="s">
         <v>93</v>
       </c>
@@ -7197,8 +8529,17 @@
       <c r="G318" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="319" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H318">
+        <v>1</v>
+      </c>
+      <c r="I318" t="s">
+        <v>320</v>
+      </c>
+      <c r="J318" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="319" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C319" s="1" t="s">
         <v>236</v>
       </c>
@@ -7214,8 +8555,11 @@
       <c r="G319" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="320" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H319">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="320" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C320" s="1" t="s">
         <v>9</v>
       </c>
@@ -7231,8 +8575,14 @@
       <c r="G320" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="321" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H320">
+        <v>1</v>
+      </c>
+      <c r="J320" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="321" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C321" s="1" t="s">
         <v>82</v>
       </c>
@@ -7248,8 +8598,11 @@
       <c r="G321" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="322" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H321">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="322" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C322" s="1" t="s">
         <v>237</v>
       </c>
@@ -7265,8 +8618,11 @@
       <c r="G322" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="323" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H322">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="323" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C323" s="1" t="s">
         <v>78</v>
       </c>
@@ -7282,8 +8638,11 @@
       <c r="G323" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="324" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H323">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="324" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C324" s="1" t="s">
         <v>79</v>
       </c>
@@ -7299,8 +8658,11 @@
       <c r="G324" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="325" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H324">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="325" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C325" s="1" t="s">
         <v>80</v>
       </c>
@@ -7316,8 +8678,11 @@
       <c r="G325" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="326" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H325">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="326" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C326" s="1" t="s">
         <v>208</v>
       </c>
@@ -7333,8 +8698,11 @@
       <c r="G326" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="327" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H326">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="327" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C327" s="1" t="s">
         <v>238</v>
       </c>
@@ -7350,8 +8718,17 @@
       <c r="G327" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="328" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H327">
+        <v>1</v>
+      </c>
+      <c r="I327" t="s">
+        <v>323</v>
+      </c>
+      <c r="J327" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="328" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C328" s="1" t="s">
         <v>212</v>
       </c>
@@ -7367,8 +8744,11 @@
       <c r="G328" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="329" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H328">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="329" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C329" s="1" t="s">
         <v>95</v>
       </c>
@@ -7384,8 +8764,11 @@
       <c r="G329" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="330" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H329">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="330" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C330" s="1" t="s">
         <v>239</v>
       </c>
@@ -7401,8 +8784,14 @@
       <c r="G330" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="331" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H330">
+        <v>1</v>
+      </c>
+      <c r="J330" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="331" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C331" s="1" t="s">
         <v>198</v>
       </c>
@@ -7418,8 +8807,17 @@
       <c r="G331" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="332" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H331">
+        <v>1</v>
+      </c>
+      <c r="I331" t="s">
+        <v>313</v>
+      </c>
+      <c r="J331" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="332" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C332" s="1" t="s">
         <v>242</v>
       </c>
@@ -7435,8 +8833,11 @@
       <c r="G332" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="333" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H332">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="333" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>286</v>
       </c>
@@ -7455,8 +8856,14 @@
       <c r="G333" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="334" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H333">
+        <v>1</v>
+      </c>
+      <c r="J333" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="334" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>286</v>
       </c>
@@ -7475,8 +8882,11 @@
       <c r="G334" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="335" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H334">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="335" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>286</v>
       </c>
@@ -7495,8 +8905,17 @@
       <c r="G335" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="336" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H335">
+        <v>1</v>
+      </c>
+      <c r="I335" t="s">
+        <v>316</v>
+      </c>
+      <c r="J335" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="336" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>286</v>
       </c>
@@ -7515,8 +8934,11 @@
       <c r="G336" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="337" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H336">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="337" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>286</v>
       </c>
@@ -7535,8 +8957,11 @@
       <c r="G337" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="338" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H337">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="338" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>286</v>
       </c>
@@ -7555,8 +8980,14 @@
       <c r="G338" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="339" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H338">
+        <v>4</v>
+      </c>
+      <c r="J338" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="339" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>286</v>
       </c>
@@ -7578,8 +9009,17 @@
       <c r="G339" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="340" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H339">
+        <v>1</v>
+      </c>
+      <c r="I339" t="s">
+        <v>320</v>
+      </c>
+      <c r="J339" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="340" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C340" s="1" t="s">
         <v>245</v>
       </c>
@@ -7595,8 +9035,11 @@
       <c r="G340" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="341" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H340">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="341" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C341" s="1" t="s">
         <v>94</v>
       </c>
@@ -7612,8 +9055,11 @@
       <c r="G341" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="342" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H341">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="342" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>286</v>
       </c>
@@ -7632,8 +9078,14 @@
       <c r="G342" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="343" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H342">
+        <v>1</v>
+      </c>
+      <c r="J342" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="343" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>286</v>
       </c>
@@ -7652,8 +9104,11 @@
       <c r="G343" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="344" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H343">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="344" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>286</v>
       </c>
@@ -7672,8 +9127,11 @@
       <c r="G344" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="345" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H344">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="345" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>286</v>
       </c>
@@ -7692,8 +9150,11 @@
       <c r="G345" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="346" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H345">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="346" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>286</v>
       </c>
@@ -7712,8 +9173,11 @@
       <c r="G346" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="347" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H346">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="347" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>286</v>
       </c>
@@ -7732,8 +9196,11 @@
       <c r="G347" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="348" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H347">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="348" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>286</v>
       </c>
@@ -7752,8 +9219,11 @@
       <c r="G348" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="349" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H348">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="349" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
         <v>286</v>
       </c>
@@ -7772,8 +9242,11 @@
       <c r="G349" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="350" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H349">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="350" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
         <v>286</v>
       </c>
@@ -7792,8 +9265,11 @@
       <c r="G350" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="351" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H350">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="351" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>286</v>
       </c>
@@ -7812,8 +9288,17 @@
       <c r="G351" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="352" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H351">
+        <v>1</v>
+      </c>
+      <c r="I351" t="s">
+        <v>323</v>
+      </c>
+      <c r="J351" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="352" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>287</v>
       </c>
@@ -7835,8 +9320,11 @@
       <c r="G352" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="353" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H352">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="353" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>287</v>
       </c>
@@ -7855,8 +9343,14 @@
       <c r="G353" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="354" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H353">
+        <v>1</v>
+      </c>
+      <c r="J353" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="354" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>287</v>
       </c>
@@ -7875,8 +9369,11 @@
       <c r="G354" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="355" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H354">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="355" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>286</v>
       </c>
@@ -7895,8 +9392,11 @@
       <c r="G355" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="356" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H355">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="356" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
         <v>286</v>
       </c>
@@ -7915,8 +9415,17 @@
       <c r="G356" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="357" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H356">
+        <v>1</v>
+      </c>
+      <c r="I356" t="s">
+        <v>325</v>
+      </c>
+      <c r="J356" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="357" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>286</v>
       </c>
@@ -7935,8 +9444,11 @@
       <c r="G357" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="358" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H357">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="358" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>286</v>
       </c>
@@ -7955,8 +9467,11 @@
       <c r="G358" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="359" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H358">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="359" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
         <v>286</v>
       </c>
@@ -7975,8 +9490,11 @@
       <c r="G359" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="360" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H359">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="360" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>286</v>
       </c>
@@ -7995,8 +9513,11 @@
       <c r="G360" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="361" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H360">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="361" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>286</v>
       </c>
@@ -8015,8 +9536,11 @@
       <c r="G361" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="362" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H361">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="362" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>286</v>
       </c>
@@ -8035,8 +9559,11 @@
       <c r="G362" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="363" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H362">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="363" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>286</v>
       </c>
@@ -8055,8 +9582,11 @@
       <c r="G363" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="364" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H363">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="364" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>286</v>
       </c>
@@ -8075,8 +9605,11 @@
       <c r="G364" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="365" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H364">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="365" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>286</v>
       </c>
@@ -8095,8 +9628,11 @@
       <c r="G365" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="366" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H365">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="366" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C366" s="1" t="s">
         <v>260</v>
       </c>
@@ -8112,8 +9648,17 @@
       <c r="G366" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="367" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H366">
+        <v>1</v>
+      </c>
+      <c r="I366" t="s">
+        <v>313</v>
+      </c>
+      <c r="J366" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="367" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C367" s="1" t="s">
         <v>263</v>
       </c>
@@ -8129,8 +9674,11 @@
       <c r="G367" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="368" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H367">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="368" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C368" s="1" t="s">
         <v>264</v>
       </c>
@@ -8146,8 +9694,11 @@
       <c r="G368" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="369" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H368">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="369" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C369" s="1" t="s">
         <v>126</v>
       </c>
@@ -8163,8 +9714,14 @@
       <c r="G369" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="370" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H369">
+        <v>1</v>
+      </c>
+      <c r="J369" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="370" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C370" s="1" t="s">
         <v>265</v>
       </c>
@@ -8180,8 +9737,11 @@
       <c r="G370" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="371" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H370">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="371" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
         <v>286</v>
       </c>
@@ -8200,8 +9760,11 @@
       <c r="G371" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="372" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H371">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="372" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B372" t="s">
         <v>298</v>
       </c>
@@ -8220,8 +9783,11 @@
       <c r="G372" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="373" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H372">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="373" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
         <v>286</v>
       </c>
@@ -8240,8 +9806,17 @@
       <c r="G373" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="374" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H373">
+        <v>1</v>
+      </c>
+      <c r="I373" t="s">
+        <v>316</v>
+      </c>
+      <c r="J373" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="374" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C374" s="1" t="s">
         <v>268</v>
       </c>
@@ -8257,8 +9832,14 @@
       <c r="G374" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="375" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H374">
+        <v>1</v>
+      </c>
+      <c r="J374" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="375" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
         <v>286</v>
       </c>
@@ -8277,8 +9858,11 @@
       <c r="G375" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="376" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H375">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="376" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
         <v>286</v>
       </c>
@@ -8297,8 +9881,17 @@
       <c r="G376" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="377" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H376">
+        <v>1</v>
+      </c>
+      <c r="I376" t="s">
+        <v>320</v>
+      </c>
+      <c r="J376" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="377" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
         <v>286</v>
       </c>
@@ -8317,8 +9910,11 @@
       <c r="G377" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="378" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H377">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="378" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
         <v>287</v>
       </c>
@@ -8337,8 +9933,11 @@
       <c r="G378" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="379" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H378">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="379" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
         <v>287</v>
       </c>
@@ -8357,8 +9956,11 @@
       <c r="G379" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="380" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H379">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="380" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
         <v>286</v>
       </c>
@@ -8377,8 +9979,11 @@
       <c r="G380" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="381" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H380">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="381" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
         <v>286</v>
       </c>
@@ -8397,8 +10002,11 @@
       <c r="G381" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="382" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H381">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="382" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
         <v>287</v>
       </c>
@@ -8417,8 +10025,17 @@
       <c r="G382" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="383" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H382">
+        <v>1</v>
+      </c>
+      <c r="I382" t="s">
+        <v>323</v>
+      </c>
+      <c r="J382" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="383" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C383" s="1" t="s">
         <v>56</v>
       </c>
@@ -8434,8 +10051,11 @@
       <c r="G383" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="384" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H383">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="384" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
         <v>287</v>
       </c>
@@ -8457,8 +10077,14 @@
       <c r="G384" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="385" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H384">
+        <v>1</v>
+      </c>
+      <c r="J384" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="385" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
         <v>287</v>
       </c>
@@ -8477,8 +10103,11 @@
       <c r="G385" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="386" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H385">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="386" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
         <v>286</v>
       </c>
@@ -8497,8 +10126,17 @@
       <c r="G386" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="387" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H386">
+        <v>1</v>
+      </c>
+      <c r="I386" t="s">
+        <v>313</v>
+      </c>
+      <c r="J386" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="387" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
         <v>286</v>
       </c>
@@ -8517,8 +10155,11 @@
       <c r="G387" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="388" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H387">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="388" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
         <v>286</v>
       </c>
@@ -8537,8 +10178,14 @@
       <c r="G388" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="389" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H388">
+        <v>1</v>
+      </c>
+      <c r="J388" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="389" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
         <v>286</v>
       </c>
@@ -8557,8 +10204,11 @@
       <c r="G389" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="390" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H389">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="390" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
         <v>286</v>
       </c>
@@ -8577,8 +10227,17 @@
       <c r="G390" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="391" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H390">
+        <v>1</v>
+      </c>
+      <c r="I390" t="s">
+        <v>316</v>
+      </c>
+      <c r="J390" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="391" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
         <v>286</v>
       </c>
@@ -8597,8 +10256,11 @@
       <c r="G391" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="392" spans="1:7" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H391">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="392" spans="1:10" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
         <v>286</v>
       </c>
@@ -8620,8 +10282,17 @@
       <c r="G392" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="393" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H392">
+        <v>1</v>
+      </c>
+      <c r="I392" t="s">
+        <v>320</v>
+      </c>
+      <c r="J392" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="393" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
         <v>286</v>
       </c>
@@ -8640,8 +10311,11 @@
       <c r="G393" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="394" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H393">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="394" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
         <v>286</v>
       </c>
@@ -8660,8 +10334,11 @@
       <c r="G394" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="395" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H394">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="395" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
         <v>286</v>
       </c>
@@ -8683,8 +10360,14 @@
       <c r="G395" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="396" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H395">
+        <v>1</v>
+      </c>
+      <c r="J395" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="396" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
         <v>286</v>
       </c>
@@ -8706,8 +10389,11 @@
       <c r="G396" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="397" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H396">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="397" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
         <v>286</v>
       </c>
@@ -8729,8 +10415,11 @@
       <c r="G397" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="398" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H397">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="398" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
         <v>286</v>
       </c>
@@ -8749,8 +10438,11 @@
       <c r="G398" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="399" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H398">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="399" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
         <v>286</v>
       </c>
@@ -8772,8 +10464,17 @@
       <c r="G399" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="400" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H399">
+        <v>1</v>
+      </c>
+      <c r="I399" t="s">
+        <v>325</v>
+      </c>
+      <c r="J399" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="400" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
         <v>286</v>
       </c>
@@ -8792,8 +10493,11 @@
       <c r="G400" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="401" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H400">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="401" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
         <v>286</v>
       </c>
@@ -8812,8 +10516,11 @@
       <c r="G401" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="402" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H401">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="402" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
         <v>286</v>
       </c>
@@ -8832,8 +10539,11 @@
       <c r="G402" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="403" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H402">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="403" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
         <v>286</v>
       </c>
@@ -8855,8 +10565,17 @@
       <c r="G403" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="404" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H403">
+        <v>5</v>
+      </c>
+      <c r="I403" t="s">
+        <v>323</v>
+      </c>
+      <c r="J403" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="404" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
         <v>286</v>
       </c>
@@ -8878,8 +10597,11 @@
       <c r="G404" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="405" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H404">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="405" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
         <v>286</v>
       </c>
@@ -8898,8 +10620,11 @@
       <c r="G405" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="406" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H405">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="406" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
         <v>286</v>
       </c>
@@ -8918,8 +10643,11 @@
       <c r="G406" s="6">
         <v>46265</v>
       </c>
-    </row>
-    <row r="407" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H406">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="407" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
         <v>286</v>
       </c>
@@ -8938,11 +10666,17 @@
       <c r="G407" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="408" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A408" t="s">
-        <v>286</v>
-      </c>
+      <c r="H407">
+        <v>1</v>
+      </c>
+      <c r="I407" t="s">
+        <v>316</v>
+      </c>
+      <c r="J407" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="408" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C408" s="1" t="s">
         <v>161</v>
       </c>
@@ -8958,8 +10692,17 @@
       <c r="G408" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="409" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H408">
+        <v>1</v>
+      </c>
+      <c r="I408" t="s">
+        <v>320</v>
+      </c>
+      <c r="J408" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="409" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C409" s="1" t="s">
         <v>158</v>
       </c>
@@ -8975,8 +10718,11 @@
       <c r="G409" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="410" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H409">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="410" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C410" s="1" t="s">
         <v>165</v>
       </c>
@@ -8992,8 +10738,14 @@
       <c r="G410" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="411" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H410">
+        <v>3</v>
+      </c>
+      <c r="J410" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="411" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C411" s="1" t="s">
         <v>166</v>
       </c>
@@ -9009,8 +10761,11 @@
       <c r="G411" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="412" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H411">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="412" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
         <v>286</v>
       </c>
@@ -9029,8 +10784,14 @@
       <c r="G412" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="413" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H412">
+        <v>5</v>
+      </c>
+      <c r="J412" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="413" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
         <v>286</v>
       </c>
@@ -9049,8 +10810,11 @@
       <c r="G413" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="414" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H413">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="414" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
         <v>290</v>
       </c>
@@ -9072,8 +10836,11 @@
       <c r="G414" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="415" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H414">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="415" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
         <v>287</v>
       </c>
@@ -9095,8 +10862,11 @@
       <c r="G415" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="416" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H415">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="416" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
         <v>286</v>
       </c>
@@ -9115,8 +10885,17 @@
       <c r="G416" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="417" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H416">
+        <v>1</v>
+      </c>
+      <c r="I416" t="s">
+        <v>325</v>
+      </c>
+      <c r="J416" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="417" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
         <v>286</v>
       </c>
@@ -9135,8 +10914,11 @@
       <c r="G417" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="418" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H417">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="418" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
         <v>286</v>
       </c>
@@ -9155,8 +10937,11 @@
       <c r="G418" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="419" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H418">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="419" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
         <v>286</v>
       </c>
@@ -9175,8 +10960,11 @@
       <c r="G419" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="420" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H419">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="420" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
         <v>286</v>
       </c>
@@ -9195,85 +10983,88 @@
       <c r="G420" s="6">
         <v>46295</v>
       </c>
-    </row>
-    <row r="421" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H420">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="421" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C421" s="1"/>
       <c r="D421" s="1"/>
       <c r="E421" s="1"/>
       <c r="F421" s="6"/>
       <c r="G421" s="6"/>
     </row>
-    <row r="422" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C422" s="1"/>
       <c r="D422" s="1"/>
       <c r="E422" s="1"/>
       <c r="F422" s="6"/>
       <c r="G422" s="6"/>
     </row>
-    <row r="423" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C423" s="1"/>
       <c r="D423" s="1"/>
       <c r="E423" s="1"/>
       <c r="F423" s="6"/>
       <c r="G423" s="6"/>
     </row>
-    <row r="424" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C424" s="1"/>
       <c r="D424" s="1"/>
       <c r="E424" s="1"/>
       <c r="F424" s="6"/>
       <c r="G424" s="6"/>
     </row>
-    <row r="425" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C425" s="1"/>
       <c r="D425" s="1"/>
       <c r="E425" s="1"/>
       <c r="F425" s="6"/>
       <c r="G425" s="6"/>
     </row>
-    <row r="426" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C426" s="1"/>
       <c r="D426" s="1"/>
       <c r="E426" s="1"/>
       <c r="F426" s="6"/>
       <c r="G426" s="6"/>
     </row>
-    <row r="427" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C427" s="1"/>
       <c r="D427" s="1"/>
       <c r="E427" s="1"/>
       <c r="F427" s="6"/>
       <c r="G427" s="6"/>
     </row>
-    <row r="428" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C428" s="1"/>
       <c r="D428" s="1"/>
       <c r="E428" s="1"/>
       <c r="F428" s="6"/>
       <c r="G428" s="6"/>
     </row>
-    <row r="429" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C429" s="1"/>
       <c r="D429" s="1"/>
       <c r="E429" s="1"/>
       <c r="F429" s="6"/>
       <c r="G429" s="6"/>
     </row>
-    <row r="430" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C430" s="1"/>
       <c r="D430" s="1"/>
       <c r="E430" s="1"/>
       <c r="F430" s="6"/>
       <c r="G430" s="6"/>
     </row>
-    <row r="431" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C431" s="1"/>
       <c r="D431" s="1"/>
       <c r="E431" s="1"/>
       <c r="F431" s="6"/>
       <c r="G431" s="6"/>
     </row>
-    <row r="432" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C432" s="1"/>
       <c r="D432" s="1"/>
       <c r="E432" s="1"/>
